--- a/data/2tbl_Gold_Fact_BudgetBranch/Branch Plan 2025.xlsx
+++ b/data/2tbl_Gold_Fact_BudgetBranch/Branch Plan 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ATK_Project\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ATK_Project\data\2tbl_Gold_Fact_BudgetBranch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51B3E62-B962-4B51-9C91-3C04063048E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31ED5ADE-307C-4155-972D-896F697D3419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25635" yWindow="1815" windowWidth="22710" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22710" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -629,7 +629,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -658,7 +658,7 @@
         <v>13</v>
       </c>
       <c r="B3" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -687,7 +687,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
@@ -716,7 +716,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
@@ -745,7 +745,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>9</v>
@@ -774,7 +774,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
@@ -803,7 +803,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>9</v>
@@ -832,7 +832,7 @@
         <v>27</v>
       </c>
       <c r="B9" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>9</v>
@@ -861,7 +861,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>9</v>
@@ -890,7 +890,7 @@
         <v>31</v>
       </c>
       <c r="B11" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>9</v>
@@ -919,7 +919,7 @@
         <v>33</v>
       </c>
       <c r="B12" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>9</v>
@@ -948,7 +948,7 @@
         <v>36</v>
       </c>
       <c r="B13" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>9</v>
@@ -977,7 +977,7 @@
         <v>38</v>
       </c>
       <c r="B14" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>9</v>
@@ -1006,7 +1006,7 @@
         <v>40</v>
       </c>
       <c r="B15" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>9</v>
@@ -1035,7 +1035,7 @@
         <v>42</v>
       </c>
       <c r="B16" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>9</v>
@@ -1064,7 +1064,7 @@
         <v>44</v>
       </c>
       <c r="B17" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>9</v>
@@ -1093,7 +1093,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>9</v>
@@ -1122,7 +1122,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>9</v>
@@ -1151,7 +1151,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>9</v>
@@ -1180,7 +1180,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>9</v>
@@ -1209,7 +1209,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>9</v>
@@ -1238,7 +1238,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>9</v>
@@ -1267,7 +1267,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>9</v>
@@ -1296,7 +1296,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>9</v>
@@ -1325,7 +1325,7 @@
         <v>29</v>
       </c>
       <c r="B26" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>9</v>
@@ -1354,7 +1354,7 @@
         <v>31</v>
       </c>
       <c r="B27" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>9</v>
@@ -1383,7 +1383,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>9</v>
@@ -1412,7 +1412,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>9</v>
@@ -1441,7 +1441,7 @@
         <v>38</v>
       </c>
       <c r="B30" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>9</v>
@@ -1470,7 +1470,7 @@
         <v>40</v>
       </c>
       <c r="B31" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>9</v>
@@ -1499,7 +1499,7 @@
         <v>42</v>
       </c>
       <c r="B32" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>9</v>
@@ -1528,7 +1528,7 @@
         <v>44</v>
       </c>
       <c r="B33" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>9</v>
@@ -1557,7 +1557,7 @@
         <v>8</v>
       </c>
       <c r="B34" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>9</v>
@@ -1586,7 +1586,7 @@
         <v>13</v>
       </c>
       <c r="B35" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>9</v>
@@ -1615,7 +1615,7 @@
         <v>16</v>
       </c>
       <c r="B36" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>9</v>
@@ -1644,7 +1644,7 @@
         <v>18</v>
       </c>
       <c r="B37" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>9</v>
@@ -1673,7 +1673,7 @@
         <v>20</v>
       </c>
       <c r="B38" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>9</v>
@@ -1702,7 +1702,7 @@
         <v>22</v>
       </c>
       <c r="B39" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>9</v>
@@ -1731,7 +1731,7 @@
         <v>25</v>
       </c>
       <c r="B40" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>9</v>
@@ -1760,7 +1760,7 @@
         <v>27</v>
       </c>
       <c r="B41" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>9</v>
@@ -1789,7 +1789,7 @@
         <v>29</v>
       </c>
       <c r="B42" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>9</v>
@@ -1818,7 +1818,7 @@
         <v>31</v>
       </c>
       <c r="B43" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>9</v>
@@ -1847,7 +1847,7 @@
         <v>33</v>
       </c>
       <c r="B44" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>9</v>
@@ -1876,7 +1876,7 @@
         <v>36</v>
       </c>
       <c r="B45" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>9</v>
@@ -1905,7 +1905,7 @@
         <v>38</v>
       </c>
       <c r="B46" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>9</v>
@@ -1934,7 +1934,7 @@
         <v>40</v>
       </c>
       <c r="B47" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>9</v>
@@ -1963,7 +1963,7 @@
         <v>42</v>
       </c>
       <c r="B48" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>9</v>
@@ -1992,7 +1992,7 @@
         <v>44</v>
       </c>
       <c r="B49" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>9</v>
@@ -2021,7 +2021,7 @@
         <v>8</v>
       </c>
       <c r="B50" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>9</v>
@@ -2050,7 +2050,7 @@
         <v>13</v>
       </c>
       <c r="B51" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>9</v>
@@ -2079,7 +2079,7 @@
         <v>16</v>
       </c>
       <c r="B52" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>9</v>
@@ -2108,7 +2108,7 @@
         <v>18</v>
       </c>
       <c r="B53" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>9</v>
@@ -2137,7 +2137,7 @@
         <v>20</v>
       </c>
       <c r="B54" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>9</v>
@@ -2166,7 +2166,7 @@
         <v>22</v>
       </c>
       <c r="B55" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>9</v>
@@ -2195,7 +2195,7 @@
         <v>25</v>
       </c>
       <c r="B56" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>9</v>
@@ -2224,7 +2224,7 @@
         <v>27</v>
       </c>
       <c r="B57" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>9</v>
@@ -2253,7 +2253,7 @@
         <v>29</v>
       </c>
       <c r="B58" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>9</v>
@@ -2282,7 +2282,7 @@
         <v>31</v>
       </c>
       <c r="B59" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>9</v>
@@ -2311,7 +2311,7 @@
         <v>33</v>
       </c>
       <c r="B60" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>9</v>
@@ -2340,7 +2340,7 @@
         <v>36</v>
       </c>
       <c r="B61" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>9</v>
@@ -2369,7 +2369,7 @@
         <v>38</v>
       </c>
       <c r="B62" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>9</v>
@@ -2398,7 +2398,7 @@
         <v>40</v>
       </c>
       <c r="B63" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>9</v>
@@ -2427,7 +2427,7 @@
         <v>42</v>
       </c>
       <c r="B64" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>9</v>
@@ -2456,7 +2456,7 @@
         <v>44</v>
       </c>
       <c r="B65" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>9</v>
@@ -2485,7 +2485,7 @@
         <v>44</v>
       </c>
       <c r="B66" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>46</v>
@@ -2514,7 +2514,7 @@
         <v>25</v>
       </c>
       <c r="B67" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>46</v>
@@ -2543,7 +2543,7 @@
         <v>18</v>
       </c>
       <c r="B68" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>46</v>
@@ -2572,7 +2572,7 @@
         <v>13</v>
       </c>
       <c r="B69" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>46</v>
@@ -2601,7 +2601,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>46</v>
@@ -2630,7 +2630,7 @@
         <v>29</v>
       </c>
       <c r="B71" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>46</v>
@@ -2659,7 +2659,7 @@
         <v>27</v>
       </c>
       <c r="B72" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>46</v>
@@ -2688,7 +2688,7 @@
         <v>22</v>
       </c>
       <c r="B73" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>46</v>
@@ -2717,7 +2717,7 @@
         <v>36</v>
       </c>
       <c r="B74" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>46</v>
@@ -2746,7 +2746,7 @@
         <v>42</v>
       </c>
       <c r="B75" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>46</v>
@@ -2775,7 +2775,7 @@
         <v>33</v>
       </c>
       <c r="B76" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>46</v>
@@ -2804,7 +2804,7 @@
         <v>20</v>
       </c>
       <c r="B77" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>46</v>
@@ -2833,7 +2833,7 @@
         <v>40</v>
       </c>
       <c r="B78" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>46</v>
@@ -2862,7 +2862,7 @@
         <v>38</v>
       </c>
       <c r="B79" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>46</v>
@@ -2891,7 +2891,7 @@
         <v>31</v>
       </c>
       <c r="B80" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>46</v>
@@ -2920,7 +2920,7 @@
         <v>8</v>
       </c>
       <c r="B81" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>46</v>
@@ -2949,7 +2949,7 @@
         <v>44</v>
       </c>
       <c r="B82" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>46</v>
@@ -2978,7 +2978,7 @@
         <v>25</v>
       </c>
       <c r="B83" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>46</v>
@@ -3007,7 +3007,7 @@
         <v>18</v>
       </c>
       <c r="B84" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>46</v>
@@ -3036,7 +3036,7 @@
         <v>13</v>
       </c>
       <c r="B85" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>46</v>
@@ -3065,7 +3065,7 @@
         <v>16</v>
       </c>
       <c r="B86" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>46</v>
@@ -3094,7 +3094,7 @@
         <v>29</v>
       </c>
       <c r="B87" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>46</v>
@@ -3123,7 +3123,7 @@
         <v>27</v>
       </c>
       <c r="B88" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>46</v>
@@ -3152,7 +3152,7 @@
         <v>22</v>
       </c>
       <c r="B89" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>46</v>
@@ -3181,7 +3181,7 @@
         <v>36</v>
       </c>
       <c r="B90" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>46</v>
@@ -3210,7 +3210,7 @@
         <v>42</v>
       </c>
       <c r="B91" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>46</v>
@@ -3239,7 +3239,7 @@
         <v>33</v>
       </c>
       <c r="B92" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>46</v>
@@ -3268,7 +3268,7 @@
         <v>20</v>
       </c>
       <c r="B93" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>46</v>
@@ -3297,7 +3297,7 @@
         <v>40</v>
       </c>
       <c r="B94" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>46</v>
@@ -3326,7 +3326,7 @@
         <v>38</v>
       </c>
       <c r="B95" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>46</v>
@@ -3355,7 +3355,7 @@
         <v>31</v>
       </c>
       <c r="B96" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>46</v>
@@ -3384,7 +3384,7 @@
         <v>8</v>
       </c>
       <c r="B97" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>46</v>
@@ -3413,7 +3413,7 @@
         <v>44</v>
       </c>
       <c r="B98" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>46</v>
@@ -3442,7 +3442,7 @@
         <v>25</v>
       </c>
       <c r="B99" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>46</v>
@@ -3471,7 +3471,7 @@
         <v>18</v>
       </c>
       <c r="B100" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>46</v>
@@ -3500,7 +3500,7 @@
         <v>13</v>
       </c>
       <c r="B101" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>46</v>
@@ -3529,7 +3529,7 @@
         <v>16</v>
       </c>
       <c r="B102" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>46</v>
@@ -3558,7 +3558,7 @@
         <v>29</v>
       </c>
       <c r="B103" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>46</v>
@@ -3587,7 +3587,7 @@
         <v>27</v>
       </c>
       <c r="B104" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>46</v>
@@ -3616,7 +3616,7 @@
         <v>22</v>
       </c>
       <c r="B105" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>46</v>
@@ -3645,7 +3645,7 @@
         <v>36</v>
       </c>
       <c r="B106" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>46</v>
@@ -3674,7 +3674,7 @@
         <v>42</v>
       </c>
       <c r="B107" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>46</v>
@@ -3703,7 +3703,7 @@
         <v>33</v>
       </c>
       <c r="B108" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>46</v>
@@ -3732,7 +3732,7 @@
         <v>20</v>
       </c>
       <c r="B109" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>46</v>
@@ -3761,7 +3761,7 @@
         <v>40</v>
       </c>
       <c r="B110" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>46</v>
@@ -3790,7 +3790,7 @@
         <v>38</v>
       </c>
       <c r="B111" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>46</v>
@@ -3819,7 +3819,7 @@
         <v>31</v>
       </c>
       <c r="B112" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>46</v>
@@ -3848,7 +3848,7 @@
         <v>8</v>
       </c>
       <c r="B113" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>46</v>
@@ -3877,7 +3877,7 @@
         <v>44</v>
       </c>
       <c r="B114" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>46</v>
@@ -3906,7 +3906,7 @@
         <v>25</v>
       </c>
       <c r="B115" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>46</v>
@@ -3935,7 +3935,7 @@
         <v>18</v>
       </c>
       <c r="B116" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>46</v>
@@ -3964,7 +3964,7 @@
         <v>13</v>
       </c>
       <c r="B117" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>46</v>
@@ -3993,7 +3993,7 @@
         <v>16</v>
       </c>
       <c r="B118" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>46</v>
@@ -4022,7 +4022,7 @@
         <v>29</v>
       </c>
       <c r="B119" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>46</v>
@@ -4051,7 +4051,7 @@
         <v>27</v>
       </c>
       <c r="B120" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>46</v>
@@ -4080,7 +4080,7 @@
         <v>22</v>
       </c>
       <c r="B121" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>46</v>
@@ -4109,7 +4109,7 @@
         <v>36</v>
       </c>
       <c r="B122" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>46</v>
@@ -4138,7 +4138,7 @@
         <v>42</v>
       </c>
       <c r="B123" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>46</v>
@@ -4167,7 +4167,7 @@
         <v>33</v>
       </c>
       <c r="B124" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>46</v>
@@ -4196,7 +4196,7 @@
         <v>20</v>
       </c>
       <c r="B125" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>46</v>
@@ -4225,7 +4225,7 @@
         <v>40</v>
       </c>
       <c r="B126" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>46</v>
@@ -4254,7 +4254,7 @@
         <v>38</v>
       </c>
       <c r="B127" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>46</v>
@@ -4283,7 +4283,7 @@
         <v>31</v>
       </c>
       <c r="B128" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>46</v>
@@ -4312,7 +4312,7 @@
         <v>8</v>
       </c>
       <c r="B129" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>46</v>
@@ -4341,7 +4341,7 @@
         <v>44</v>
       </c>
       <c r="B130" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>46</v>
@@ -4370,7 +4370,7 @@
         <v>25</v>
       </c>
       <c r="B131" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>46</v>
@@ -4399,7 +4399,7 @@
         <v>18</v>
       </c>
       <c r="B132" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>46</v>
@@ -4428,7 +4428,7 @@
         <v>13</v>
       </c>
       <c r="B133" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>46</v>
@@ -4457,7 +4457,7 @@
         <v>16</v>
       </c>
       <c r="B134" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>46</v>
@@ -4486,7 +4486,7 @@
         <v>29</v>
       </c>
       <c r="B135" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>46</v>
@@ -4515,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="B136" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>46</v>
@@ -4544,7 +4544,7 @@
         <v>22</v>
       </c>
       <c r="B137" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>46</v>
@@ -4573,7 +4573,7 @@
         <v>36</v>
       </c>
       <c r="B138" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>46</v>
@@ -4602,7 +4602,7 @@
         <v>42</v>
       </c>
       <c r="B139" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>46</v>
@@ -4631,7 +4631,7 @@
         <v>33</v>
       </c>
       <c r="B140" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>46</v>
@@ -4660,7 +4660,7 @@
         <v>20</v>
       </c>
       <c r="B141" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>46</v>
@@ -4689,7 +4689,7 @@
         <v>40</v>
       </c>
       <c r="B142" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>46</v>
@@ -4718,7 +4718,7 @@
         <v>38</v>
       </c>
       <c r="B143" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>46</v>
@@ -4747,7 +4747,7 @@
         <v>31</v>
       </c>
       <c r="B144" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>46</v>
@@ -4776,7 +4776,7 @@
         <v>8</v>
       </c>
       <c r="B145" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>46</v>
@@ -4805,7 +4805,7 @@
         <v>49</v>
       </c>
       <c r="B146" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>46</v>
@@ -4834,7 +4834,7 @@
         <v>44</v>
       </c>
       <c r="B147" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>46</v>
@@ -4863,7 +4863,7 @@
         <v>25</v>
       </c>
       <c r="B148" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>46</v>
@@ -4892,7 +4892,7 @@
         <v>18</v>
       </c>
       <c r="B149" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>46</v>
@@ -4921,7 +4921,7 @@
         <v>13</v>
       </c>
       <c r="B150" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>46</v>
@@ -4950,7 +4950,7 @@
         <v>16</v>
       </c>
       <c r="B151" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>46</v>
@@ -4979,7 +4979,7 @@
         <v>29</v>
       </c>
       <c r="B152" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>46</v>
@@ -5008,7 +5008,7 @@
         <v>27</v>
       </c>
       <c r="B153" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>46</v>
@@ -5037,7 +5037,7 @@
         <v>22</v>
       </c>
       <c r="B154" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>46</v>
@@ -5066,7 +5066,7 @@
         <v>36</v>
       </c>
       <c r="B155" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>46</v>
@@ -5095,7 +5095,7 @@
         <v>42</v>
       </c>
       <c r="B156" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>46</v>
@@ -5124,7 +5124,7 @@
         <v>33</v>
       </c>
       <c r="B157" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>46</v>
@@ -5153,7 +5153,7 @@
         <v>20</v>
       </c>
       <c r="B158" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>46</v>
@@ -5182,7 +5182,7 @@
         <v>40</v>
       </c>
       <c r="B159" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>46</v>
@@ -5211,7 +5211,7 @@
         <v>38</v>
       </c>
       <c r="B160" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>46</v>
@@ -5240,7 +5240,7 @@
         <v>31</v>
       </c>
       <c r="B161" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>46</v>
@@ -5269,7 +5269,7 @@
         <v>8</v>
       </c>
       <c r="B162" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>46</v>
@@ -5298,7 +5298,7 @@
         <v>49</v>
       </c>
       <c r="B163" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>46</v>
@@ -5327,7 +5327,7 @@
         <v>44</v>
       </c>
       <c r="B164" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>46</v>
@@ -5356,7 +5356,7 @@
         <v>25</v>
       </c>
       <c r="B165" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>46</v>
@@ -5385,7 +5385,7 @@
         <v>18</v>
       </c>
       <c r="B166" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>46</v>
@@ -5414,7 +5414,7 @@
         <v>13</v>
       </c>
       <c r="B167" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>46</v>
@@ -5443,7 +5443,7 @@
         <v>16</v>
       </c>
       <c r="B168" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>46</v>
@@ -5472,7 +5472,7 @@
         <v>29</v>
       </c>
       <c r="B169" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>46</v>
@@ -5501,7 +5501,7 @@
         <v>27</v>
       </c>
       <c r="B170" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>46</v>
@@ -5530,7 +5530,7 @@
         <v>22</v>
       </c>
       <c r="B171" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>46</v>
@@ -5559,7 +5559,7 @@
         <v>36</v>
       </c>
       <c r="B172" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>46</v>
@@ -5588,7 +5588,7 @@
         <v>42</v>
       </c>
       <c r="B173" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>46</v>
@@ -5617,7 +5617,7 @@
         <v>33</v>
       </c>
       <c r="B174" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>46</v>
@@ -5646,7 +5646,7 @@
         <v>20</v>
       </c>
       <c r="B175" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>46</v>
@@ -5675,7 +5675,7 @@
         <v>40</v>
       </c>
       <c r="B176" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>46</v>
@@ -5704,7 +5704,7 @@
         <v>38</v>
       </c>
       <c r="B177" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>46</v>
@@ -5733,7 +5733,7 @@
         <v>31</v>
       </c>
       <c r="B178" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>46</v>
@@ -5762,7 +5762,7 @@
         <v>8</v>
       </c>
       <c r="B179" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>46</v>
@@ -5791,7 +5791,7 @@
         <v>49</v>
       </c>
       <c r="B180" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>46</v>
@@ -5820,7 +5820,7 @@
         <v>44</v>
       </c>
       <c r="B181" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>46</v>
@@ -5849,7 +5849,7 @@
         <v>25</v>
       </c>
       <c r="B182" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>46</v>
@@ -5878,7 +5878,7 @@
         <v>18</v>
       </c>
       <c r="B183" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>46</v>
@@ -5907,7 +5907,7 @@
         <v>13</v>
       </c>
       <c r="B184" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>46</v>
@@ -5936,7 +5936,7 @@
         <v>16</v>
       </c>
       <c r="B185" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>46</v>
@@ -5965,7 +5965,7 @@
         <v>29</v>
       </c>
       <c r="B186" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>46</v>
@@ -5994,7 +5994,7 @@
         <v>27</v>
       </c>
       <c r="B187" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>46</v>
@@ -6023,7 +6023,7 @@
         <v>22</v>
       </c>
       <c r="B188" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>46</v>
@@ -6052,7 +6052,7 @@
         <v>36</v>
       </c>
       <c r="B189" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>46</v>
@@ -6081,7 +6081,7 @@
         <v>42</v>
       </c>
       <c r="B190" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>46</v>
@@ -6110,7 +6110,7 @@
         <v>33</v>
       </c>
       <c r="B191" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>46</v>
@@ -6139,7 +6139,7 @@
         <v>20</v>
       </c>
       <c r="B192" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>46</v>
@@ -6168,7 +6168,7 @@
         <v>40</v>
       </c>
       <c r="B193" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>46</v>
@@ -6197,7 +6197,7 @@
         <v>38</v>
       </c>
       <c r="B194" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>46</v>
@@ -6226,7 +6226,7 @@
         <v>31</v>
       </c>
       <c r="B195" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>46</v>
@@ -6255,7 +6255,7 @@
         <v>8</v>
       </c>
       <c r="B196" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>46</v>
@@ -6284,7 +6284,7 @@
         <v>49</v>
       </c>
       <c r="B197" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>46</v>
@@ -6313,7 +6313,7 @@
         <v>44</v>
       </c>
       <c r="B198" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>46</v>
@@ -6342,7 +6342,7 @@
         <v>25</v>
       </c>
       <c r="B199" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>46</v>
@@ -6371,7 +6371,7 @@
         <v>18</v>
       </c>
       <c r="B200" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>46</v>
@@ -6400,7 +6400,7 @@
         <v>13</v>
       </c>
       <c r="B201" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>46</v>
@@ -6429,7 +6429,7 @@
         <v>16</v>
       </c>
       <c r="B202" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>46</v>
@@ -6458,7 +6458,7 @@
         <v>29</v>
       </c>
       <c r="B203" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>46</v>
@@ -6487,7 +6487,7 @@
         <v>27</v>
       </c>
       <c r="B204" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>46</v>
@@ -6516,7 +6516,7 @@
         <v>22</v>
       </c>
       <c r="B205" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>46</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="B206" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>46</v>
@@ -6574,7 +6574,7 @@
         <v>42</v>
       </c>
       <c r="B207" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>46</v>
@@ -6603,7 +6603,7 @@
         <v>33</v>
       </c>
       <c r="B208" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>46</v>
@@ -6632,7 +6632,7 @@
         <v>20</v>
       </c>
       <c r="B209" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>46</v>
@@ -6661,7 +6661,7 @@
         <v>40</v>
       </c>
       <c r="B210" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>46</v>
@@ -6690,7 +6690,7 @@
         <v>38</v>
       </c>
       <c r="B211" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>46</v>
@@ -6719,7 +6719,7 @@
         <v>31</v>
       </c>
       <c r="B212" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>46</v>
@@ -6748,7 +6748,7 @@
         <v>8</v>
       </c>
       <c r="B213" s="4">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>46</v>
@@ -6777,7 +6777,7 @@
         <v>44</v>
       </c>
       <c r="B214" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>46</v>
@@ -6806,7 +6806,7 @@
         <v>25</v>
       </c>
       <c r="B215" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>46</v>
@@ -6835,7 +6835,7 @@
         <v>18</v>
       </c>
       <c r="B216" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>46</v>
@@ -6864,7 +6864,7 @@
         <v>13</v>
       </c>
       <c r="B217" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>46</v>
@@ -6893,7 +6893,7 @@
         <v>16</v>
       </c>
       <c r="B218" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>46</v>
@@ -6922,7 +6922,7 @@
         <v>29</v>
       </c>
       <c r="B219" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>46</v>
@@ -6951,7 +6951,7 @@
         <v>27</v>
       </c>
       <c r="B220" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>46</v>
@@ -6980,7 +6980,7 @@
         <v>22</v>
       </c>
       <c r="B221" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>46</v>
@@ -7009,7 +7009,7 @@
         <v>36</v>
       </c>
       <c r="B222" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>46</v>
@@ -7038,7 +7038,7 @@
         <v>42</v>
       </c>
       <c r="B223" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>46</v>
@@ -7067,7 +7067,7 @@
         <v>33</v>
       </c>
       <c r="B224" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>46</v>
@@ -7096,7 +7096,7 @@
         <v>20</v>
       </c>
       <c r="B225" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>46</v>
@@ -7125,7 +7125,7 @@
         <v>40</v>
       </c>
       <c r="B226" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>46</v>
@@ -7154,7 +7154,7 @@
         <v>38</v>
       </c>
       <c r="B227" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>46</v>
@@ -7183,7 +7183,7 @@
         <v>31</v>
       </c>
       <c r="B228" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>46</v>
@@ -7212,7 +7212,7 @@
         <v>8</v>
       </c>
       <c r="B229" s="4">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>46</v>
@@ -7241,7 +7241,7 @@
         <v>44</v>
       </c>
       <c r="B230" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>46</v>
@@ -7270,7 +7270,7 @@
         <v>25</v>
       </c>
       <c r="B231" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>46</v>
@@ -7299,7 +7299,7 @@
         <v>18</v>
       </c>
       <c r="B232" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>46</v>
@@ -7328,7 +7328,7 @@
         <v>13</v>
       </c>
       <c r="B233" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>46</v>
@@ -7357,7 +7357,7 @@
         <v>16</v>
       </c>
       <c r="B234" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>46</v>
@@ -7386,7 +7386,7 @@
         <v>29</v>
       </c>
       <c r="B235" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>46</v>
@@ -7415,7 +7415,7 @@
         <v>27</v>
       </c>
       <c r="B236" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>46</v>
@@ -7444,7 +7444,7 @@
         <v>22</v>
       </c>
       <c r="B237" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>46</v>
@@ -7473,7 +7473,7 @@
         <v>36</v>
       </c>
       <c r="B238" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>46</v>
@@ -7502,7 +7502,7 @@
         <v>42</v>
       </c>
       <c r="B239" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>46</v>
@@ -7531,7 +7531,7 @@
         <v>33</v>
       </c>
       <c r="B240" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>46</v>
@@ -7560,7 +7560,7 @@
         <v>20</v>
       </c>
       <c r="B241" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>46</v>
@@ -7589,7 +7589,7 @@
         <v>40</v>
       </c>
       <c r="B242" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>46</v>
@@ -7618,7 +7618,7 @@
         <v>38</v>
       </c>
       <c r="B243" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>46</v>
@@ -7647,7 +7647,7 @@
         <v>31</v>
       </c>
       <c r="B244" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>46</v>
@@ -7676,7 +7676,7 @@
         <v>8</v>
       </c>
       <c r="B245" s="4">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>46</v>
@@ -7705,7 +7705,7 @@
         <v>44</v>
       </c>
       <c r="B246" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>46</v>
@@ -7734,7 +7734,7 @@
         <v>25</v>
       </c>
       <c r="B247" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>46</v>
@@ -7763,7 +7763,7 @@
         <v>18</v>
       </c>
       <c r="B248" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>46</v>
@@ -7792,7 +7792,7 @@
         <v>13</v>
       </c>
       <c r="B249" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>46</v>
@@ -7821,7 +7821,7 @@
         <v>16</v>
       </c>
       <c r="B250" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>46</v>
@@ -7850,7 +7850,7 @@
         <v>29</v>
       </c>
       <c r="B251" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>46</v>
@@ -7879,7 +7879,7 @@
         <v>27</v>
       </c>
       <c r="B252" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>46</v>
@@ -7908,7 +7908,7 @@
         <v>22</v>
       </c>
       <c r="B253" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>46</v>
@@ -7937,7 +7937,7 @@
         <v>36</v>
       </c>
       <c r="B254" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>46</v>
@@ -7966,7 +7966,7 @@
         <v>42</v>
       </c>
       <c r="B255" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>46</v>
@@ -7995,7 +7995,7 @@
         <v>33</v>
       </c>
       <c r="B256" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>46</v>
@@ -8024,7 +8024,7 @@
         <v>20</v>
       </c>
       <c r="B257" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>46</v>
@@ -8053,7 +8053,7 @@
         <v>40</v>
       </c>
       <c r="B258" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>46</v>
@@ -8082,7 +8082,7 @@
         <v>38</v>
       </c>
       <c r="B259" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>46</v>
@@ -8111,7 +8111,7 @@
         <v>31</v>
       </c>
       <c r="B260" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>46</v>
@@ -8140,7 +8140,7 @@
         <v>8</v>
       </c>
       <c r="B261" s="4">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>46</v>
@@ -8169,7 +8169,7 @@
         <v>44</v>
       </c>
       <c r="B262" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>46</v>
@@ -8198,7 +8198,7 @@
         <v>25</v>
       </c>
       <c r="B263" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>46</v>
@@ -8227,7 +8227,7 @@
         <v>18</v>
       </c>
       <c r="B264" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>46</v>
@@ -8256,7 +8256,7 @@
         <v>13</v>
       </c>
       <c r="B265" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>46</v>
@@ -8285,7 +8285,7 @@
         <v>29</v>
       </c>
       <c r="B266" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>46</v>
@@ -8314,7 +8314,7 @@
         <v>27</v>
       </c>
       <c r="B267" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>46</v>
@@ -8343,7 +8343,7 @@
         <v>22</v>
       </c>
       <c r="B268" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>46</v>
@@ -8372,7 +8372,7 @@
         <v>36</v>
       </c>
       <c r="B269" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>46</v>
@@ -8401,7 +8401,7 @@
         <v>42</v>
       </c>
       <c r="B270" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>46</v>
@@ -8430,7 +8430,7 @@
         <v>33</v>
       </c>
       <c r="B271" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>46</v>
@@ -8459,7 +8459,7 @@
         <v>20</v>
       </c>
       <c r="B272" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>46</v>
@@ -8488,7 +8488,7 @@
         <v>40</v>
       </c>
       <c r="B273" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>46</v>
@@ -8517,7 +8517,7 @@
         <v>38</v>
       </c>
       <c r="B274" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>46</v>
@@ -8546,7 +8546,7 @@
         <v>31</v>
       </c>
       <c r="B275" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>46</v>
@@ -8575,7 +8575,7 @@
         <v>8</v>
       </c>
       <c r="B276" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>46</v>
@@ -8604,7 +8604,7 @@
         <v>53</v>
       </c>
       <c r="B277" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>46</v>
@@ -8633,7 +8633,7 @@
         <v>44</v>
       </c>
       <c r="B278" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>46</v>
@@ -8662,7 +8662,7 @@
         <v>25</v>
       </c>
       <c r="B279" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>46</v>
@@ -8691,7 +8691,7 @@
         <v>18</v>
       </c>
       <c r="B280" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>46</v>
@@ -8720,7 +8720,7 @@
         <v>13</v>
       </c>
       <c r="B281" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>46</v>
@@ -8749,7 +8749,7 @@
         <v>29</v>
       </c>
       <c r="B282" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>46</v>
@@ -8778,7 +8778,7 @@
         <v>27</v>
       </c>
       <c r="B283" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>46</v>
@@ -8807,7 +8807,7 @@
         <v>22</v>
       </c>
       <c r="B284" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>46</v>
@@ -8836,7 +8836,7 @@
         <v>36</v>
       </c>
       <c r="B285" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>46</v>
@@ -8865,7 +8865,7 @@
         <v>42</v>
       </c>
       <c r="B286" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>46</v>
@@ -8894,7 +8894,7 @@
         <v>33</v>
       </c>
       <c r="B287" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>46</v>
@@ -8923,7 +8923,7 @@
         <v>20</v>
       </c>
       <c r="B288" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>46</v>
@@ -8952,7 +8952,7 @@
         <v>40</v>
       </c>
       <c r="B289" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>46</v>
@@ -8981,7 +8981,7 @@
         <v>38</v>
       </c>
       <c r="B290" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>46</v>
@@ -9010,7 +9010,7 @@
         <v>31</v>
       </c>
       <c r="B291" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>46</v>
@@ -9039,7 +9039,7 @@
         <v>8</v>
       </c>
       <c r="B292" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>46</v>
@@ -9068,7 +9068,7 @@
         <v>53</v>
       </c>
       <c r="B293" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>46</v>
@@ -9097,7 +9097,7 @@
         <v>44</v>
       </c>
       <c r="B294" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>46</v>
@@ -9126,7 +9126,7 @@
         <v>25</v>
       </c>
       <c r="B295" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>46</v>
@@ -9155,7 +9155,7 @@
         <v>18</v>
       </c>
       <c r="B296" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>46</v>
@@ -9184,7 +9184,7 @@
         <v>13</v>
       </c>
       <c r="B297" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>46</v>
@@ -9213,7 +9213,7 @@
         <v>29</v>
       </c>
       <c r="B298" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>46</v>
@@ -9242,7 +9242,7 @@
         <v>27</v>
       </c>
       <c r="B299" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>46</v>
@@ -9271,7 +9271,7 @@
         <v>22</v>
       </c>
       <c r="B300" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>46</v>
@@ -9300,7 +9300,7 @@
         <v>36</v>
       </c>
       <c r="B301" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>46</v>
@@ -9329,7 +9329,7 @@
         <v>42</v>
       </c>
       <c r="B302" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>46</v>
@@ -9358,7 +9358,7 @@
         <v>33</v>
       </c>
       <c r="B303" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>46</v>
@@ -9387,7 +9387,7 @@
         <v>20</v>
       </c>
       <c r="B304" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>46</v>
@@ -9416,7 +9416,7 @@
         <v>40</v>
       </c>
       <c r="B305" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>46</v>
@@ -9445,7 +9445,7 @@
         <v>38</v>
       </c>
       <c r="B306" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>46</v>
@@ -9474,7 +9474,7 @@
         <v>31</v>
       </c>
       <c r="B307" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>46</v>
@@ -9503,7 +9503,7 @@
         <v>8</v>
       </c>
       <c r="B308" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>46</v>
@@ -9532,7 +9532,7 @@
         <v>53</v>
       </c>
       <c r="B309" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>46</v>
@@ -9561,7 +9561,7 @@
         <v>44</v>
       </c>
       <c r="B310" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>46</v>
@@ -9590,7 +9590,7 @@
         <v>25</v>
       </c>
       <c r="B311" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>46</v>
@@ -9619,7 +9619,7 @@
         <v>18</v>
       </c>
       <c r="B312" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>46</v>
@@ -9648,7 +9648,7 @@
         <v>13</v>
       </c>
       <c r="B313" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>46</v>
@@ -9677,7 +9677,7 @@
         <v>29</v>
       </c>
       <c r="B314" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>46</v>
@@ -9706,7 +9706,7 @@
         <v>27</v>
       </c>
       <c r="B315" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>46</v>
@@ -9735,7 +9735,7 @@
         <v>22</v>
       </c>
       <c r="B316" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>46</v>
@@ -9764,7 +9764,7 @@
         <v>36</v>
       </c>
       <c r="B317" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>46</v>
@@ -9793,7 +9793,7 @@
         <v>42</v>
       </c>
       <c r="B318" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>46</v>
@@ -9822,7 +9822,7 @@
         <v>33</v>
       </c>
       <c r="B319" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>46</v>
@@ -9851,7 +9851,7 @@
         <v>20</v>
       </c>
       <c r="B320" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>46</v>
@@ -9880,7 +9880,7 @@
         <v>40</v>
       </c>
       <c r="B321" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>46</v>
@@ -9909,7 +9909,7 @@
         <v>38</v>
       </c>
       <c r="B322" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>46</v>
@@ -9938,7 +9938,7 @@
         <v>31</v>
       </c>
       <c r="B323" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>46</v>
@@ -9967,7 +9967,7 @@
         <v>8</v>
       </c>
       <c r="B324" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>46</v>
@@ -9996,7 +9996,7 @@
         <v>53</v>
       </c>
       <c r="B325" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>46</v>
@@ -10025,7 +10025,7 @@
         <v>54</v>
       </c>
       <c r="B326" s="1">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>46</v>
@@ -10054,7 +10054,7 @@
         <v>54</v>
       </c>
       <c r="B327" s="1">
-        <v>45961</v>
+        <v>45931</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>46</v>
@@ -10083,7 +10083,7 @@
         <v>54</v>
       </c>
       <c r="B328" s="1">
-        <v>45991</v>
+        <v>45962</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>46</v>
@@ -10112,7 +10112,7 @@
         <v>54</v>
       </c>
       <c r="B329" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>46</v>

--- a/data/2tbl_Gold_Fact_BudgetBranch/Branch Plan 2025.xlsx
+++ b/data/2tbl_Gold_Fact_BudgetBranch/Branch Plan 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ATK_Project\data\2tbl_Gold_Fact_BudgetBranch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0787EE32-ACD3-451B-A35B-B9E776D68B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1901421-7913-4B9E-9136-2F1D81A49D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25245" yWindow="1920" windowWidth="22710" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/2tbl_Gold_Fact_BudgetBranch/Branch Plan 2025.xlsx
+++ b/data/2tbl_Gold_Fact_BudgetBranch/Branch Plan 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ATK_Project\data\2tbl_Gold_Fact_BudgetBranch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1901421-7913-4B9E-9136-2F1D81A49D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02923B62-589D-463A-AEFC-1FFC572F3EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25245" yWindow="1920" windowWidth="22710" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -615,7 +615,7 @@
     <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
     <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="33.140625" bestFit="1" customWidth="1"/>
